--- a/GD.codexalgorithm_contents_sheet.xlsx
+++ b/GD.codexalgorithm_contents_sheet.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="142">
   <si>
     <t>Timestamp</t>
   </si>
@@ -117,7 +117,7 @@
 current_position += velocity</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1cSNXtQERv5_ZtRAhWVex3m6NGt9AP636</t>
+    <t>../Images/BasicMovementAlgorithm_graph.png</t>
   </si>
   <si>
     <t>This algorithm can be used in various games where NPCs need to move towards targets. For example, in a strategy game, NPC units can move towards enemy units or objectives using this movement algorithm.
@@ -139,8 +139,7 @@
   </si>
   <si>
     <t>A kinematic seeking movement algorithm is designed to determine the movement of a character based on its current position and orientation. Unlike dynamic movement algorithms, which consider forces and acceleration, kinematic algorithms directly calculate the desired velocity to achieve a particular movement. The primary inputs for this algorithm are the character's current position and orientation, while the output is the velocity vector that indicates the direction and speed of movement.
-The kinematic seek behaviour is designed to move a character towards a target. It requires the character's static data (current position) and the target's static data (target position) as inputs. The algorithm calculates the direction from the character to the target and sets a velocity along this line. Orientation values are generally ignored. 
-It is importatn to realise that although this algorithm will make sure the character will keep aiming at the target position, the fact that it will keep a constant maximum speed mean that it will keep overshooting it and result in a oshillating behaviour when close to its target.</t>
+The kinematic seek behaviour is designed to move a character towards a target. It requires the character's static data (current position) and the target's static data (target position) as inputs. The algorithm calculates the direction from the character to the target and sets a velocity along this line. Orientation values are generally ignored.</t>
   </si>
   <si>
     <t>Non-player character NPC</t>
@@ -248,23 +247,10 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">This system is based on the kinematic seek movement algorithm and tries to solve its flaws.
+    <t>This system is based on the kinematic seek movement algorithm and tries to solve its flaws.
 Satisfaction Radius: The kinematic arrive behaviour includes a satisfaction radius, which defines how close the character needs to be to the target before it stops moving. The kinematic seek behaviour does not have this feature and moves the character directly to the target without slowing down.
 Smooth Stopping: The kinematic arrive behaviour calculates a velocity that gradually decreases as the character approaches the target, ensuring a smooth stop. In contrast, the kinematic seek behaviour moves the character at full speed towards the target without considering deceleration.
-Time to Target: The kinematic arrive behaviour incorporates a timeToTarget constant to control how quickly the character should reach the target. This adds a level of control over the movement speed as the character gets closer to the target.
-More resources can be found on:
-AI for games: third edition by Ian Millington
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.amazon.com/AI-Games-Third-Ian-Millington/dp/1138483974</t>
-    </r>
+Time to Target: The kinematic arrive behaviour incorporates a timeToTarget constant to control how quickly the character should reach the target. This adds a level of control over the movement speed as the character gets closer to the target.</t>
   </si>
   <si>
     <t>Kinematic wandering moevement</t>
@@ -301,13 +287,108 @@
 </t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1CtGaGOexFIC5nTXrT3vWrVKbOF5SNIyM</t>
-  </si>
-  <si>
-    <t>Test enty</t>
-  </si>
-  <si>
-    <t>Test entry text</t>
+    <t>../Images/KinematicWanderMovement_graph - Codex Algorithm.png</t>
+  </si>
+  <si>
+    <t>Pac-Man Ghosts</t>
+  </si>
+  <si>
+    <t>In the original Pac-Man, the ghosts (also called monsters) have distinct behaviours. Each ghost has a unique personality and movement pattern designed to challenge the player in different ways. Despite appearing random, their movements are governed by precise rules.
+General Behaviour
+Modes: Ghosts switch between two main modes:
+Chase Mode: They actively pursue Pac-Man based on their specific targeting logic.
+Scatter Mode: They move to their predefined "home corners" on the map and patrol there.
+Frightened Mode: When Pac-Man eats a Power Pellet, ghosts turn blue and move randomly, allowing Pac-Man to eat them for points.
+Collision Mechanics: If Pac-Man collides with a ghost in chase or scatter mode, he loses a life. If a ghost is in frightened mode, Pac-Man "eats" the ghost, sending it back to the ghost house to respawn.
+Ghost Personalities
+Each ghost has a unique targeting behaviour:
+Blinky (Red):
+Nicknamed "Chaser."
+Targets Pac-Man's current position directly.
+Becomes faster as more dots are eaten, earning the nickname "Cruise Elroy.
+Pinky (Pink):
+Nicknamed "Ambusher."
+Tries to move to a position four tiles ahead of Pac-Man in the direction he’s currently facing.
+Sometimes appears to "cut off" Pac-Man.
+Inky (Cyan):
+Nicknamed "Fickle."
+Targets a position determined by both Blinky's position and Pac-Man's position, creating complex behaviour.
+The target tile is calculated as a reflection of Blinky's position relative to a tile two tiles ahead of Pac-Man.
+Clyde (Orange):
+Nicknamed "Pokey."
+Alternates between chasing Pac-Man and retreating to his home corner.
+If Clyde is more than eight tiles away from Pac-Man, he chases. If closer, he moves toward his scatter corner.</t>
+  </si>
+  <si>
+    <t>Finite state machine (FSM)</t>
+  </si>
+  <si>
+    <t>Pathfinding</t>
+  </si>
+  <si>
+    <t>Arcade and rhythm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">initialize ghost with (name, color, scatterCorner)
+set mode = "scatter"
+while game_running:
+    if mode == "scatter":
+        move_towards(scatterCorner)
+    else if mode == "chase":
+        if ghost.name == "Blinky":
+            target = pacman.position
+        else if ghost.name == "Pinky":
+            target = position_ahead_of(pacman, 4)
+        else if ghost.name == "Inky":
+            vector = position_ahead_of(pacman, 2) - blinky.position
+            target = position_ahead_of(pacman, 2) + vector
+        else if ghost.name == "Clyde":
+            if distance_to(pacman) &gt; 8:
+                target = pacman.position
+            else:
+                target = scatterCorner
+        move_towards(target)
+    if pacman_eats_power_pellet:
+        mode = "frightened"
+        move_randomly()
+    if collision_with(pacman):
+        if mode == "frightened":
+            ghost_respawn()
+        else:
+            pacman_lose_life()
+    check_mode_switch_timer()
+end
+</t>
+  </si>
+  <si>
+    <t>../Images/pac-man_ghost behaviour.png, ../Images/pac-man_ghost patrol patterns.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The Pac-Man Dossier" by Jamey Pittman:
+This extensive guide delves into the game's mechanics, including a thorough examination of the ghost AI.
+It offers detailed explanations of the pathfinding logic, state transitions, and the specific behaviours that give each ghost its unique personality.
+Read the dossier here:
+https://designoriented.net/blog/2015/06/09/201569pac-man-design-deterministic-and-random-ghosts/
+"Pac-Man Ghost AI Explained" Video:
+For a visual and auditory explanation, this video breaks down the algorithms and logic that dictate ghost behaviour in an accessible format.
+Watch the video here:
+https://www.youtube.com/watch?v=ataGotQ7ir8 </t>
+  </si>
+  <si>
+    <t>Convai</t>
+  </si>
+  <si>
+    <t>Convai enables AI characters in games and virtual worlds to have human-like conversation capabilities and more. With Convai, developers can add a backstory, knowledge bank, voice, and overall intelligence to their character assets to converse naturally with players and carry out actions.
+Convai includes the complete conversation pipeline, which includes Speech Recognition, Language Understanding, and Generation, Text-to-Speech, Text-to-Action, Lipsync. Convai focuses on bringing characters that are as life-like as possible and can be directed by any developer!
+Highlights:
+Intelligent real-time open-ended conversation capabilities, enabling natural and dynamic interactions.
+Actions: Characters can understand the environment and perform actions based on conversation, verbal commands, and events, opening up new possibilities.
+Knowledge Bank: You can add potentially unlimited knowledge for your characters, making them an expert at a topic or grounding them in the lore of the world and their backstories.
+Intelligent Animations: Integrated with Lip-Sync and custom facial and body animations with conversation flow.
+Avatar Integrations: Integrated out-of-the-box with the most popular avatar platforms like Reallusion Character Creator 4 and Ready Player Me. Compatible with all model families.
+AR/VR/MR Support: Characters support AR-VR-MR platforms.
+Text or Talk: You can use text or voice input to talk to your characters.
+Production Ready: The asset can be deployed to hundreds of users (under our commercial agreement).</t>
   </si>
   <si>
     <t>Machine learning</t>
@@ -316,59 +397,257 @@
     <t>Neural network</t>
   </si>
   <si>
+    <t>Narrative</t>
+  </si>
+  <si>
+    <t>Is run on a server, Needs internet connection, Runs on PC</t>
+  </si>
+  <si>
+    <t>../Images/conv-ai.png</t>
+  </si>
+  <si>
+    <t>AI in alien isolation</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>AI that models</t>
+  </si>
+  <si>
+    <t>Strategic opponent</t>
+  </si>
+  <si>
+    <t>Tactical and strategic</t>
+  </si>
+  <si>
+    <t>Simulation</t>
+  </si>
+  <si>
+    <t>Adventure RPG</t>
+  </si>
+  <si>
+    <t>Is run locally, Runs on PC, Runs on Playstation, Runs on Xbox</t>
+  </si>
+  <si>
+    <t>AI of Forza drivers</t>
+  </si>
+  <si>
+    <t>Reinforcement learning</t>
+  </si>
+  <si>
+    <t>Sports and racing</t>
+  </si>
+  <si>
+    <t>Racing sim</t>
+  </si>
+  <si>
+    <t>No man's sky procedural generation</t>
+  </si>
+  <si>
+    <t>Generative AI</t>
+  </si>
+  <si>
     <t>AI that creates</t>
   </si>
   <si>
+    <t>Procedural generation</t>
+  </si>
+  <si>
+    <t>Procedural content generation</t>
+  </si>
+  <si>
+    <t>Adventure</t>
+  </si>
+  <si>
+    <t>Is run locally, Needs internet connection, Runs on PC, Runs on Playstation, Runs on Xbox</t>
+  </si>
+  <si>
+    <t>The Sims (Sim AI)</t>
+  </si>
+  <si>
+    <t>Simulates autonomous behaviour for virtual people.</t>
+  </si>
+  <si>
+    <t>Behaviour tree</t>
+  </si>
+  <si>
+    <t>Decision making</t>
+  </si>
+  <si>
+    <t>Role-playing</t>
+  </si>
+  <si>
+    <t>Is run locally, Runs on PC, Runs on Playstation, Runs on Xbox, Runs on handheld devices</t>
+  </si>
+  <si>
+    <t>Left 4 Dead (AI Director)</t>
+  </si>
+  <si>
+    <t>Dynamic difficulty adjustment and enemy spawning based on player performance.</t>
+  </si>
+  <si>
+    <t>State machine</t>
+  </si>
+  <si>
+    <t>Managing experience</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>First-person shooter</t>
+  </si>
+  <si>
+    <t>Is run locally, Runs on PC</t>
+  </si>
+  <si>
+    <t>Middle-earth: Shadow of Mordor (Nemesis System)</t>
+  </si>
+  <si>
+    <t>racks player interactions with procedurally generated enemies.</t>
+  </si>
+  <si>
+    <t>Halo (Combat AI)</t>
+  </si>
+  <si>
+    <t>Each enemy type has distinct tactical behaviours.</t>
+  </si>
+  <si>
+    <t>Is run locally, Runs on PC, Runs on Playstation, Runs on Xbox, Runs on mobile</t>
+  </si>
+  <si>
+    <t>F.E.A.R. (Combat AI)</t>
+  </si>
+  <si>
+    <t>Highly praised squad-based AI for engaging enemies.</t>
+  </si>
+  <si>
+    <t>Metal Gear Solid (Enemy AI)</t>
+  </si>
+  <si>
+    <t>Guards respond to noise, footprints, and player presence.</t>
+  </si>
+  <si>
+    <t>Third-person shooter</t>
+  </si>
+  <si>
+    <t>Chessmaster (Chess AI)</t>
+  </si>
+  <si>
+    <t>Implements different play styles and difficulty levels.</t>
+  </si>
+  <si>
+    <t>Strategy</t>
+  </si>
+  <si>
+    <t>Turn-based</t>
+  </si>
+  <si>
+    <t>Is run on a server, Needs internet connection, Runs on PC, Runs on Playstation, Runs on Xbox, Runs on mobile, Runs on handheld devices</t>
+  </si>
+  <si>
+    <t>Zerg Swarm AI (StarCraft)</t>
+  </si>
+  <si>
+    <t>Uses a state machine combined with pathfinding algorithms (like A* or potential fields) to simulate swarm-like behavior and tactical group movement. The Zerg AI adapts to the player's actions, sending units in groups to overwhelm opponents.</t>
+  </si>
+  <si>
+    <t>Giant Enemy Crab AI (Shenmue)</t>
+  </si>
+  <si>
+    <t>A symbolic decision tree AI system used for complex battle interactions. The AI assesses player proximity and attacks based on predefined patterns to simulate a more "intelligent" creature.</t>
+  </si>
+  <si>
+    <t>Decision tree</t>
+  </si>
+  <si>
+    <t>The Predator AI (Alien vs. Predator)</t>
+  </si>
+  <si>
+    <t>This AI uses decision trees and state machines to control the predator's hunting behavior, including tracking, ambushing, and combat strategies based on player actions and distance.</t>
+  </si>
+  <si>
+    <t>Civilization AI (Civilization series)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rule-based AI that simulates diplomatic, military, and economic decision-making. Each civilization’s AI follows a predefined set of rules based on its personality traits (aggressive, peaceful, etc.) and adapts strategies based on the player's actions and game state.
+</t>
+  </si>
+  <si>
+    <t>Strategy RPG</t>
+  </si>
+  <si>
+    <t>Evolving AI Agents (Black &amp; White)</t>
+  </si>
+  <si>
+    <t>Uses a genetic algorithm to simulate evolving creatures that learn behaviors through interaction with the player and the environment. The creatures’ decisions are influenced by both their inherited traits and learned experiences.</t>
+  </si>
+  <si>
+    <t>Learning</t>
+  </si>
+  <si>
+    <t>Is run on a server, Needs internet connection, Runs on PC, Runs on Playstation, Runs on Xbox</t>
+  </si>
+  <si>
+    <t>Bully AI (Grand Theft Auto: San Andreas)</t>
+  </si>
+  <si>
+    <t>Rule-based system with an influence map to simulate pedestrian behavior. NPCs react based on the player's actions, creating emergent interactions such as fights, traffic accidents, and social dynamics.</t>
+  </si>
+  <si>
+    <t>Flocking Behavior AI (Minecraft)</t>
+  </si>
+  <si>
+    <t>Used in controlling groups of animals (like birds or sheep), this AI uses Boids algorithm to simulate natural flocking behavior. The animals move together in groups with basic steering rules, like avoiding separation and maintaining cohesion.</t>
+  </si>
+  <si>
+    <t>Enemy AI (The Legend of Zelda: Ocarina of Time)</t>
+  </si>
+  <si>
+    <t>State machine-based AI that handles enemy behavior, such as moving toward the player, attacking, or retreating. Each enemy has different states and transitions between them based on player interaction, health, and proximity.</t>
+  </si>
+  <si>
+    <t>Goat AI (The Witcher 3)</t>
+  </si>
+  <si>
+    <t>Uses pathfinding algorithms to control animals like goats, where the AI adapts to environmental obstacles, ensuring natural movement behavior in large open worlds.</t>
+  </si>
+  <si>
+    <t>Pathfinding system</t>
+  </si>
+  <si>
+    <t>Evolving Enemy Behavior (Dead Rising)</t>
+  </si>
+  <si>
+    <t>Uses reactive AI and emergent behaviors where enemies change tactics based on time of day, player actions, and environmental conditions (e.g., more aggressive at night).</t>
+  </si>
+  <si>
+    <t>AI Companions (BioShock Infinite - Elizabeth)</t>
+  </si>
+  <si>
+    <t>Pathfinding and decision tree-based system, where Elizabeth follows the player and provides support during combat by selecting the right time to toss supplies, open tears, or assist in battle.</t>
+  </si>
+  <si>
+    <t>Dynamic Encounter AI (Dying Light)</t>
+  </si>
+  <si>
+    <t>Uses a scripting system and state machine to control the day-night cycle, where zombie behavior drastically changes based on time of day—more aggressive and dynamic during the night.</t>
+  </si>
+  <si>
+    <t>Autonomous Vehicle AI (Watch Dogs)</t>
+  </si>
+  <si>
+    <t>Traffic simulation AI that controls civilian vehicles, ensuring that they follow traffic rules, react to obstacles, and avoid collisions. It also includes behavior for vehicles interacting with the player.</t>
+  </si>
+  <si>
+    <t>Mind Control AI (Control)</t>
+  </si>
+  <si>
+    <t>Implements symbolic AI with a belief-desire-intention (BDI) model, controlling NPCs who act based on the player's influence, power, and choices within the game's narrative.</t>
+  </si>
+  <si>
     <t>Real-time rendering</t>
-  </si>
-  <si>
-    <t>Learning</t>
-  </si>
-  <si>
-    <t>Simulation</t>
-  </si>
-  <si>
-    <t>Is run locally, Runs on PC, Runs on Playstation, Runs on handheld devices</t>
-  </si>
-  <si>
-    <t>Multiple images</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>State machine</t>
-  </si>
-  <si>
-    <t>AI that models</t>
-  </si>
-  <si>
-    <t>Online matchmaking</t>
-  </si>
-  <si>
-    <t>Pathfinding</t>
-  </si>
-  <si>
-    <t>Adventure</t>
-  </si>
-  <si>
-    <t>Hack &amp; slash</t>
-  </si>
-  <si>
-    <t>Is run on a server, Needs internet connection, Runs on PC, Runs on Xbox</t>
-  </si>
-  <si>
-    <t>Nononononono</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1Rc4H7X4OBt5quC0sZhLk-LRcHehwmMbi, https://drive.google.com/open?id=1Kt9InWv44QPlD2D4VafvF5CKe848JBjh, https://drive.google.com/open?id=18GpkGoVIWo7BdlbwdYxB6ubdM8TewgiP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other links and examples here
-https://www.youtube.com/watch?v=dQw4w9WgXcQ </t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1cjcimb7S5Z-d75KhwGpepb99NgcSkoKX, https://drive.google.com/open?id=1hVhvSltcFRAY4fUhBrvUCBqU92BK3_Zt</t>
   </si>
 </sst>
 </file>
@@ -378,7 +657,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -392,22 +671,12 @@
     </font>
     <font>
       <u/>
-      <color rgb="FF434343"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <u/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
-      <color rgb="FF0000FF"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
   </fonts>
@@ -419,7 +688,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -535,6 +804,20 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
@@ -579,14 +862,11 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -601,10 +881,7 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -613,26 +890,44 @@
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,7 +987,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Q8" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Q56" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="17">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="System name" id="2"/>
@@ -941,400 +1236,2422 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>45660.62919707176</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="I2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>6.0</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>1.0</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9">
+      <c r="A3" s="7">
         <v>45661.68384380787</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="10" t="s">
+      <c r="I3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="8">
         <v>6.0</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="8">
         <v>1.0</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="O3" s="9"/>
+      <c r="P3" s="8" t="s">
         <v>34</v>
       </c>
+      <c r="Q3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="11">
+      <c r="A4" s="4">
         <v>45661.690393275465</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="12" t="s">
+      <c r="I4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="5">
         <v>6.0</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="5">
         <v>1.0</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="O4" s="11"/>
+      <c r="P4" s="5" t="s">
         <v>34</v>
       </c>
+      <c r="Q4" s="12"/>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="7">
         <v>45661.69956625</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="10" t="s">
+      <c r="I5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="8">
         <v>6.0</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="8">
         <v>1.0</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="O5" s="9"/>
+      <c r="P5" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="Q5" s="10"/>
     </row>
     <row r="6">
-      <c r="A6" s="11">
+      <c r="A6" s="4">
         <v>45661.70633385416</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="12" t="s">
+      <c r="I6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="5">
         <v>6.0</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="5">
         <v>1.0</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="O6" s="14" t="s">
+      <c r="O6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="P6" s="5" t="s">
         <v>34</v>
       </c>
+      <c r="Q6" s="12"/>
     </row>
     <row r="7">
-      <c r="A7" s="9">
-        <v>45672.671838738424</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="7">
+        <v>45684.5740897338</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="I7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="K7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="8">
+        <v>7.0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="O7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="P7" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="10" t="s">
+      <c r="Q7" s="10"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13">
+        <v>45684.590590486114</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="10">
+      <c r="C8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="M8" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16">
+        <v>45684.59649457176</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="17">
+        <v>10.0</v>
+      </c>
+      <c r="M9" s="17">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13">
+        <v>45684.597505150465</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="M10" s="14">
         <v>4.0</v>
       </c>
-      <c r="M7" s="10">
+    </row>
+    <row r="11">
+      <c r="A11" s="16">
+        <v>45684.59914146991</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="M11" s="17">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13">
+        <v>45684.60510847223</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="M12" s="14">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16">
+        <v>45684.605959733795</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="L13" s="17">
         <v>8.0</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15">
-        <v>45675.60260814815</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="M13" s="17">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13">
+        <v>45684.606631006944</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M14" s="14">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16">
+        <v>45684.60733172453</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="M15" s="17">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13">
+        <v>45684.607788090274</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="M16" s="14">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16">
+        <v>45684.60839152778</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="M17" s="17">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13">
+        <v>45684.60918318287</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="16" t="s">
+      <c r="E18" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L18" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="M18" s="14">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16">
+        <v>45684.6122675</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L19" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="M19" s="17">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13">
+        <v>45684.61297810185</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="L20" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="M20" s="14">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16">
+        <v>45684.61369174768</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L21" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="M21" s="17">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13">
+        <v>45684.614309745375</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L22" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M22" s="14">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16">
+        <v>45684.615590925925</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="L23" s="17">
+        <v>8.0</v>
+      </c>
+      <c r="M23" s="17">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13">
+        <v>45684.61625390046</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="M24" s="14">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16">
+        <v>45684.617078587966</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="M25" s="17">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13">
+        <v>45684.617629988425</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="M26" s="14">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16">
+        <v>45684.61808251157</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="M27" s="17">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13">
+        <v>45684.618901168986</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L28" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="M28" s="14">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16">
+        <v>45684.61945407407</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L29" s="17">
+        <v>8.0</v>
+      </c>
+      <c r="M29" s="17">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13">
+        <v>45684.61994938657</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="M30" s="14">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16">
+        <v>45684.62049341435</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L31" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="M31" s="17">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13">
+        <v>45684.62124706019</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="L32" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="M32" s="14">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16">
+        <v>45684.59649457176</v>
+      </c>
+      <c r="B33" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="C33" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="D33" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="16">
+      <c r="G33" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L33" s="17">
+        <v>10.0</v>
+      </c>
+      <c r="M33" s="17">
+        <v>5.0</v>
+      </c>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="10"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13">
+        <v>45684.597505150465</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L34" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="M34" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="12"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16">
+        <v>45684.59914146991</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L35" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="M35" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="10"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13">
+        <v>45684.60510847223</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L36" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="M36" s="14">
         <v>3.0</v>
       </c>
-      <c r="M8" s="16">
+      <c r="P36" s="11"/>
+      <c r="Q36" s="12"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16">
+        <v>45684.605959733795</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="L37" s="17">
         <v>8.0</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="M37" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="10"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13">
+        <v>45684.606631006944</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L38" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M38" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="12"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16">
+        <v>45684.60733172453</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L39" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="M39" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="10"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13">
+        <v>45684.607788090274</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="H40" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q8" s="17" t="s">
+      <c r="I40" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L40" s="14">
+        <v>9.0</v>
+      </c>
+      <c r="M40" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="12"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16">
+        <v>45684.60839152778</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="M41" s="17">
+        <v>3.0</v>
+      </c>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="10"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13">
+        <v>45684.60918318287</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L42" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="M42" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="12"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16">
+        <v>45684.6122675</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L43" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="M43" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="10"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13">
+        <v>45684.61297810185</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="L44" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="M44" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="12"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16">
+        <v>45684.61369174768</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L45" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="M45" s="17">
+        <v>5.0</v>
+      </c>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="10"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13">
+        <v>45684.614309745375</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L46" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="M46" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="12"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16">
+        <v>45684.615590925925</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I47" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="L47" s="17">
+        <v>8.0</v>
+      </c>
+      <c r="M47" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="10"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13">
+        <v>45684.61625390046</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J48" s="14" t="s">
         <v>67</v>
       </c>
+      <c r="K48" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="M48" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="12"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="16">
+        <v>45684.617078587966</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="M49" s="17">
+        <v>2.0</v>
+      </c>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="10"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13">
+        <v>45684.617629988425</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L50" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="M50" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="12"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="16">
+        <v>45684.61808251157</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I51" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J51" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K51" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L51" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="M51" s="17">
+        <v>2.0</v>
+      </c>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="10"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13">
+        <v>45684.618901168986</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L52" s="14">
+        <v>8.0</v>
+      </c>
+      <c r="M52" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="12"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16">
+        <v>45684.61945407407</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J53" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K53" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L53" s="17">
+        <v>8.0</v>
+      </c>
+      <c r="M53" s="17">
+        <v>5.0</v>
+      </c>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="10"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13">
+        <v>45684.61994938657</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L54" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="M54" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="12"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16">
+        <v>45684.62049341435</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I55" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J55" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L55" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="M55" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="P55" s="9"/>
+      <c r="Q55" s="10"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="18">
+        <v>45684.62124706019</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="H56" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="I56" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J56" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="L56" s="19">
+        <v>9.0</v>
+      </c>
+      <c r="M56" s="19">
+        <v>9.0</v>
+      </c>
+      <c r="P56" s="20"/>
+      <c r="Q56" s="21"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="O2"/>
-    <hyperlink r:id="rId2" ref="Q2"/>
-    <hyperlink r:id="rId3" ref="P5"/>
-    <hyperlink r:id="rId4" ref="O6"/>
+    <hyperlink r:id="rId1" ref="Q2"/>
+    <hyperlink r:id="rId2" ref="O8"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/GD.codexalgorithm_contents_sheet.xlsx
+++ b/GD.codexalgorithm_contents_sheet.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="166">
   <si>
     <t>Timestamp</t>
   </si>
@@ -502,7 +502,7 @@
     <t>Is run locally, Runs on PC</t>
   </si>
   <si>
-    <t>Middle-earth: Shadow of Mordor (Nemesis System)</t>
+    <t>Middle-earth Shadow of Mordor (Nemesis System)</t>
   </si>
   <si>
     <t>racks player interactions with procedurally generated enemies.</t>
@@ -590,7 +590,7 @@
     <t>Is run on a server, Needs internet connection, Runs on PC, Runs on Playstation, Runs on Xbox</t>
   </si>
   <si>
-    <t>Bully AI (Grand Theft Auto: San Andreas)</t>
+    <t>Bully AI (Grand Theft Auto San Andreas)</t>
   </si>
   <si>
     <t>Rule-based system with an influence map to simulate pedestrian behavior. NPCs react based on the player's actions, creating emergent interactions such as fights, traffic accidents, and social dynamics.</t>
@@ -602,7 +602,7 @@
     <t>Used in controlling groups of animals (like birds or sheep), this AI uses Boids algorithm to simulate natural flocking behavior. The animals move together in groups with basic steering rules, like avoiding separation and maintaining cohesion.</t>
   </si>
   <si>
-    <t>Enemy AI (The Legend of Zelda: Ocarina of Time)</t>
+    <t>Enemy AI (The Legend of Zelda Ocarina of Time)</t>
   </si>
   <si>
     <t>State machine-based AI that handles enemy behavior, such as moving toward the player, attacking, or retreating. Each enemy has different states and transitions between them based on player interaction, health, and proximity.</t>
@@ -648,6 +648,78 @@
   </si>
   <si>
     <t>Real-time rendering</t>
+  </si>
+  <si>
+    <t>AI in alien isolation 2</t>
+  </si>
+  <si>
+    <t>AI of Forza drivers 2</t>
+  </si>
+  <si>
+    <t>No man's sky procedural generation 2</t>
+  </si>
+  <si>
+    <t>The Sims (Sim AI)2</t>
+  </si>
+  <si>
+    <t>Left 4 Dead (AI Director)2</t>
+  </si>
+  <si>
+    <t>Middle-earth Shadow of Mordor (Nemesis System)2</t>
+  </si>
+  <si>
+    <t>Halo (Combat AI)2</t>
+  </si>
+  <si>
+    <t>F.E.A.R. (Combat AI)2</t>
+  </si>
+  <si>
+    <t>Metal Gear Solid (Enemy AI)2</t>
+  </si>
+  <si>
+    <t>Chessmaster (Chess AI)2</t>
+  </si>
+  <si>
+    <t>Zerg Swarm AI (StarCraft)2</t>
+  </si>
+  <si>
+    <t>Giant Enemy Crab AI (Shenmue)2</t>
+  </si>
+  <si>
+    <t>The Predator AI (Alien vs. Predator)2</t>
+  </si>
+  <si>
+    <t>Civilization AI (Civilization series)2</t>
+  </si>
+  <si>
+    <t>Evolving AI Agents (Black &amp; White)2</t>
+  </si>
+  <si>
+    <t>Bully AI (Grand Theft Auto San Andreas)2</t>
+  </si>
+  <si>
+    <t>Flocking Behavior AI (Minecraft)2</t>
+  </si>
+  <si>
+    <t>Enemy AI (The Legend of Zelda Ocarina of Time)2</t>
+  </si>
+  <si>
+    <t>Goat AI (The Witcher 3)2</t>
+  </si>
+  <si>
+    <t>Evolving Enemy Behavior (Dead Rising)2</t>
+  </si>
+  <si>
+    <t>AI Companions (BioShock Infinite - Elizabeth)2</t>
+  </si>
+  <si>
+    <t>Dynamic Encounter AI (Dying Light)2</t>
+  </si>
+  <si>
+    <t>Autonomous Vehicle AI (Watch Dogs)2</t>
+  </si>
+  <si>
+    <t>Mind Control AI (Control)2</t>
   </si>
 </sst>
 </file>
@@ -2617,7 +2689,7 @@
         <v>45684.59649457176</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>62</v>
@@ -2660,7 +2732,7 @@
         <v>45684.597505150465</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>62</v>
@@ -2703,7 +2775,7 @@
         <v>45684.59914146991</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>62</v>
@@ -2746,7 +2818,7 @@
         <v>45684.60510847223</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>81</v>
@@ -2789,7 +2861,7 @@
         <v>45684.605959733795</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>87</v>
@@ -2832,7 +2904,7 @@
         <v>45684.606631006944</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>94</v>
@@ -2875,7 +2947,7 @@
         <v>45684.60733172453</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>96</v>
@@ -2918,7 +2990,7 @@
         <v>45684.607788090274</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>99</v>
@@ -2961,7 +3033,7 @@
         <v>45684.60839152778</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>101</v>
@@ -3004,7 +3076,7 @@
         <v>45684.60918318287</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>104</v>
@@ -3047,7 +3119,7 @@
         <v>45684.6122675</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>109</v>
@@ -3090,7 +3162,7 @@
         <v>45684.61297810185</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>111</v>
@@ -3133,7 +3205,7 @@
         <v>45684.61369174768</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>114</v>
@@ -3176,7 +3248,7 @@
         <v>45684.614309745375</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>116</v>
@@ -3219,7 +3291,7 @@
         <v>45684.615590925925</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>119</v>
@@ -3262,7 +3334,7 @@
         <v>45684.61625390046</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>123</v>
@@ -3305,7 +3377,7 @@
         <v>45684.617078587966</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>125</v>
@@ -3348,7 +3420,7 @@
         <v>45684.617629988425</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>127</v>
@@ -3391,7 +3463,7 @@
         <v>45684.61808251157</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>129</v>
@@ -3434,7 +3506,7 @@
         <v>45684.618901168986</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="C52" s="14" t="s">
         <v>132</v>
@@ -3477,7 +3549,7 @@
         <v>45684.61945407407</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>134</v>
@@ -3520,7 +3592,7 @@
         <v>45684.61994938657</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>136</v>
@@ -3563,7 +3635,7 @@
         <v>45684.62049341435</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>138</v>
@@ -3606,7 +3678,7 @@
         <v>45684.62124706019</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>140</v>
